--- a/data/trans_dic/IP07_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>71,16%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>77,87%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>83,13%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>65,88%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>71,5%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>78,31%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>87,14%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>76,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>71,16%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,13%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,41; 77,45</t>
+          <t>65,36; 76,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>72,14; 83,58</t>
+          <t>72,18; 83,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,29; 91,69</t>
+          <t>77,56; 87,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,51; 82,1</t>
+          <t>49,95; 75,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,99; 77,03</t>
+          <t>64,95; 77,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,17; 83,52</t>
+          <t>71,77; 83,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,9; 88,16</t>
+          <t>81,61; 91,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51,08; 76,46</t>
+          <t>69,45; 81,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,82; 75,03</t>
+          <t>67,01; 75,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73,76; 81,59</t>
+          <t>74,04; 82,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81,08; 88,52</t>
+          <t>81,14; 88,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>60,47; 76,44</t>
+          <t>63,04; 76,66</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>72,88%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>71,42%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>74,1%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>73,08%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>70,67%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>86,08%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>74,17%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>72,88%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>71,42%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>85,67%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,83%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,18; 77,89</t>
+          <t>68,15; 77,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,5; 75,49</t>
+          <t>66,0; 75,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>81,91; 89,65</t>
+          <t>81,5; 89,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,84; 79,5</t>
+          <t>68,76; 79,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>67,8; 77,7</t>
+          <t>68,09; 77,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,42; 76,43</t>
+          <t>65,65; 75,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,84; 89,54</t>
+          <t>81,68; 89,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>70,1; 79,85</t>
+          <t>69,74; 80,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>69,4; 76,37</t>
+          <t>69,6; 76,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>67,57; 74,52</t>
+          <t>67,64; 74,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83,09; 88,42</t>
+          <t>82,64; 88,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>70,29; 78,25</t>
+          <t>70,86; 78,34</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79,39%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84,64%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>79,78%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>79,89%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>77,27%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>87,97%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>83,12%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,39%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,64%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>79,57%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,62; 84,49</t>
+          <t>77,54; 87,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,98; 82,16</t>
+          <t>73,79; 84,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,48; 91,53</t>
+          <t>79,97; 88,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>77,57; 90,71</t>
+          <t>74,01; 85,21</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,49; 87,31</t>
+          <t>74,38; 84,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,47; 84,35</t>
+          <t>71,0; 82,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,88; 89,02</t>
+          <t>83,85; 91,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71,41; 83,94</t>
+          <t>73,39; 84,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77,74; 84,97</t>
+          <t>77,74; 85,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>74,42; 81,95</t>
+          <t>74,41; 81,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83,27; 89,02</t>
+          <t>83,21; 88,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76,18; 85,63</t>
+          <t>75,7; 83,27</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>79,96%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>72,18%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>89,18%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>81,29%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>84,35%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>76,23%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>87,74%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75,11%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>72,18%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>89,18%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>79,67; 88,21</t>
+          <t>75,03; 84,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>71,38; 80,93</t>
+          <t>66,32; 77,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,64; 91,15</t>
+          <t>85,12; 92,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69,0; 80,17</t>
+          <t>75,87; 85,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>75,28; 84,27</t>
+          <t>79,58; 87,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,69; 77,11</t>
+          <t>70,94; 80,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,69; 92,38</t>
+          <t>83,36; 91,37</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>76,01; 85,99</t>
+          <t>68,56; 80,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78,64; 85,09</t>
+          <t>78,94; 85,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70,5; 77,81</t>
+          <t>70,25; 77,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85,64; 91,0</t>
+          <t>85,51; 90,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,8; 81,8</t>
+          <t>74,07; 81,56</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>76,68%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>74,72%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>85,91%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75,73%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>77,6%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>75,25%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>87,19%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77,29%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>76,68%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>74,72%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,03; 80,03</t>
+          <t>73,77; 79,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>72,53; 77,8</t>
+          <t>71,91; 77,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84,71; 89,13</t>
+          <t>83,79; 88,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74,08; 80,84</t>
+          <t>71,89; 78,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>74,05; 79,23</t>
+          <t>74,85; 79,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,88; 77,31</t>
+          <t>72,36; 78,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,67; 88,01</t>
+          <t>85,05; 89,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,76; 78,85</t>
+          <t>73,47; 79,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>75,32; 78,93</t>
+          <t>75,46; 79,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73,06; 76,72</t>
+          <t>73,08; 76,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85,09; 87,93</t>
+          <t>85,07; 87,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>73,96; 78,72</t>
+          <t>73,47; 78,1</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>147</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>143</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>108353</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>119801</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>122452</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82953</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>99188</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>108558</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>115924</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>89128</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>108353</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>119801</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>122452</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>94120</t>
+          <t>92359</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>183248</t>
+          <t>175312</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90736; 107450</t>
+          <t>99517; 117065</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>100007; 115860</t>
+          <t>111039; 127975</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109473; 121966</t>
+          <t>114250; 129299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81524; 96285</t>
+          <t>62894; 94496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98950; 117280</t>
+          <t>90106; 107763</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>111026; 128488</t>
+          <t>99494; 115796</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>113282; 129871</t>
+          <t>108557; 122172</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>71724; 107354</t>
+          <t>84088; 98557</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>194450; 218325</t>
+          <t>194989; 219162</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>215729; 238624</t>
+          <t>216547; 240381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>227307; 248146</t>
+          <t>227452; 247366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>155824; 196977</t>
+          <t>155684; 189343</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>227</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>285</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>211</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>153638</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>158826</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>191014</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>175775</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>142634</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>145841</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>177414</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>141305</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>153638</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>158826</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>191014</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>192454</t>
+          <t>139712</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>333760</t>
+          <t>315487</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>133069; 152013</t>
+          <t>143647; 163415</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>135155; 155783</t>
+          <t>146774; 168772</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>168805; 184774</t>
+          <t>181701; 198722</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125427; 151463</t>
+          <t>163112; 188427</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>142917; 163791</t>
+          <t>132878; 151129</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>147711; 169968</t>
+          <t>135482; 156088</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>182472; 199631</t>
+          <t>168342; 183980</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>178780; 203639</t>
+          <t>128617; 148772</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>281753; 310018</t>
+          <t>282528; 310465</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289716; 319512</t>
+          <t>290002; 320085</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>356489; 379378</t>
+          <t>354559; 378780</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>313174; 348637</t>
+          <t>298767; 330276</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>188</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>225</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>179</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>124378</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>132258</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>141069</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>134309</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>110101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>119524</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>158254</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>124378</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>132258</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>141069</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>145571</t>
+          <t>124619</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>303825</t>
+          <t>258929</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>101464; 116448</t>
+          <t>116041; 131265</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>109795; 127090</t>
+          <t>122931; 140495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129093; 141541</t>
+          <t>133285; 147466</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>147691; 172721</t>
+          <t>124597; 143435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>115965; 130666</t>
+          <t>102502; 116779</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>124056; 140516</t>
+          <t>109829; 127380</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>133144; 148366</t>
+          <t>129653; 141956</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>132304; 155535</t>
+          <t>115256; 133004</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>223479; 244266</t>
+          <t>223492; 245448</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>239084; 263279</t>
+          <t>239053; 262770</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>267565; 286031</t>
+          <t>267349; 285585</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>286215; 321704</t>
+          <t>246330; 270943</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>208</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>246</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>179</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>165656</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>149431</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>182902</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>137683</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>176549</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>159716</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>180761</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>126158</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>165656</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>149431</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>182902</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>147534</t>
+          <t>124555</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>273693</t>
+          <t>262238</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>166760; 184640</t>
+          <t>155452; 174790</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>149550; 169555</t>
+          <t>137299; 159691</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>172324; 187784</t>
+          <t>174579; 189383</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>115888; 134657</t>
+          <t>128501; 145290</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>155968; 174600</t>
+          <t>166581; 184054</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>138054; 159621</t>
+          <t>148623; 168782</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>173684; 189456</t>
+          <t>171730; 188247</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>137762; 155855</t>
+          <t>114602; 133856</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>327536; 354381</t>
+          <t>328777; 354712</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>293650; 324115</t>
+          <t>292607; 322842</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>352086; 374097</t>
+          <t>351520; 372983</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>261218; 285658</t>
+          <t>249262; 274463</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>801</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>749</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>770</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>918</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>712</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>830</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>801</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>749</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>552024</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>560316</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>637436</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>530720</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>528471</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>533639</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>610128</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>514845</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>552024</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>560316</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>637436</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>579679</t>
+          <t>481245</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1094524</t>
+          <t>1011965</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>510969; 544993</t>
+          <t>531032; 569418</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>514352; 551741</t>
+          <t>539212; 577892</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>592800; 623724</t>
+          <t>621765; 653037</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>493501; 538549</t>
+          <t>503826; 550622</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>533092; 570402</t>
+          <t>509734; 544114</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>538961; 579701</t>
+          <t>513145; 553843</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>620838; 653042</t>
+          <t>595178; 622956</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>546755; 600807</t>
+          <t>462596; 497545</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1055193; 1105701</t>
+          <t>1057138; 1107039</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1065909; 1119379</t>
+          <t>1066253; 1120739</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1226851; 1267830</t>
+          <t>1226504; 1268462</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1056234; 1124260</t>
+          <t>977554; 1039155</t>
         </is>
       </c>
     </row>
